--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\G Drive\Code\flyby\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{017E8D6C-1B7A-492A-B11D-6A7356A3ED43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A462E59-242D-40E8-9DF0-7334A2D096AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="592" xr2:uid="{2C9189CC-F63B-451A-B99F-40FF8A7E7B0A}"/>
+    <workbookView xWindow="15744" yWindow="0" windowWidth="7296" windowHeight="12360" tabRatio="592" xr2:uid="{2C9189CC-F63B-451A-B99F-40FF8A7E7B0A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -213,7 +213,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -252,13 +252,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor rgb="FFFF0000"/>
+        <bgColor theme="4" tint="0.79995117038483843"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor rgb="FFFF0000"/>
         <bgColor auto="1"/>
       </patternFill>
     </fill>
@@ -290,7 +296,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
@@ -371,20 +377,35 @@
     <xf numFmtId="164" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="1" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1108,647 +1129,647 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:7" s="28" customFormat="1">
-      <c r="A17" s="1">
+    <row r="17" spans="1:7" s="16" customFormat="1">
+      <c r="A17" s="17">
         <v>46029</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="3">
+      <c r="B17" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="19">
         <v>0.3034722222222222</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="19">
         <v>0.45277777777777778</v>
       </c>
-      <c r="F17" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G17" s="4" t="s">
+      <c r="F17" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="G17" s="15" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:7" s="28" customFormat="1">
-      <c r="A18" s="29">
+    <row r="18" spans="1:7" s="16" customFormat="1">
+      <c r="A18" s="11">
         <v>46029</v>
       </c>
-      <c r="B18" s="30" t="s">
+      <c r="B18" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="31">
+      <c r="C18" s="13">
         <v>0.49583333333333335</v>
       </c>
-      <c r="D18" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18" s="31">
+      <c r="D18" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="13">
         <v>0.6381944444444444</v>
       </c>
-      <c r="F18" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="G18" s="33" t="s">
+      <c r="F18" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="G18" s="26" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="1">
+    <row r="19" spans="1:7" s="16" customFormat="1">
+      <c r="A19" s="17">
         <v>46037</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" s="3">
+      <c r="B19" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="19">
         <v>0.31527777777777777</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="19">
         <v>0.47708333333333336</v>
       </c>
-      <c r="F19" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G19" s="4" t="s">
+      <c r="F19" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="G19" s="15" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="6">
+    <row r="20" spans="1:7" s="16" customFormat="1">
+      <c r="A20" s="11">
         <v>46037</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="13">
         <v>0.50972222222222219</v>
       </c>
-      <c r="D20" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E20" s="8">
+      <c r="D20" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="13">
         <v>0.65</v>
       </c>
-      <c r="F20" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="G20" s="9" t="s">
+      <c r="F20" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="G20" s="26" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="1">
+    <row r="21" spans="1:7" s="16" customFormat="1">
+      <c r="A21" s="17">
         <v>46038</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" s="3">
+      <c r="B21" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="19">
         <v>0.30555555555555558</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="F21" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G21" s="4" t="s">
+      <c r="F21" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="G21" s="15" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="1">
+    <row r="22" spans="1:7" s="16" customFormat="1">
+      <c r="A22" s="17">
         <v>46030</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" s="3">
+      <c r="B22" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="19">
         <v>0.48958333333333331</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="19">
         <v>0.65138888888888891</v>
       </c>
-      <c r="F22" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G22" s="4" t="s">
+      <c r="F22" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="G22" s="15" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="6">
+    <row r="23" spans="1:7" s="16" customFormat="1">
+      <c r="A23" s="11">
         <v>46030</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="8">
+      <c r="C23" s="13">
         <v>0.68055555555555558</v>
       </c>
-      <c r="D23" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E23" s="8">
+      <c r="D23" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="13">
         <v>0.82291666666666663</v>
       </c>
-      <c r="F23" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="G23" s="9" t="s">
+      <c r="F23" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="G23" s="26" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="1">
+    <row r="24" spans="1:7" s="16" customFormat="1">
+      <c r="A24" s="17">
         <v>46043</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" s="3">
+      <c r="B24" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="19">
         <v>0.44097222222222221</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="19">
         <v>0.64583333333333337</v>
       </c>
-      <c r="F24" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G24" s="4" t="s">
+      <c r="F24" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="G24" s="15" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="6">
+    <row r="25" spans="1:7" s="16" customFormat="1">
+      <c r="A25" s="11">
         <v>46043</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="8">
+      <c r="C25" s="13">
         <v>0.67361111111111116</v>
       </c>
-      <c r="D25" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E25" s="8">
+      <c r="D25" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="13">
         <v>0.85763888888888884</v>
       </c>
-      <c r="F25" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="G25" s="9" t="s">
+      <c r="F25" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="G25" s="26" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="1">
+    <row r="26" spans="1:7" s="16" customFormat="1">
+      <c r="A26" s="17">
         <v>46008</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C26" s="3">
+      <c r="B26" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="19">
         <v>0.67222222222222228</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="E26" s="3">
+      <c r="E26" s="19">
         <v>0.77847222222222223</v>
       </c>
-      <c r="F26" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G26" s="4" t="s">
+      <c r="F26" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="G26" s="15" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="6">
+    <row r="27" spans="1:7" s="16" customFormat="1">
+      <c r="A27" s="11">
         <v>46008</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="8">
+      <c r="C27" s="13">
         <v>0.82361111111111107</v>
       </c>
-      <c r="D27" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E27" s="8">
+      <c r="D27" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" s="13">
         <v>0.92777777777777781</v>
       </c>
-      <c r="F27" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="G27" s="9" t="s">
+      <c r="F27" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="G27" s="26" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="1">
+    <row r="28" spans="1:7" s="16" customFormat="1">
+      <c r="A28" s="17">
         <v>46013</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C28" s="3">
+      <c r="B28" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="19">
         <v>0.43819444444444444</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E28" s="3">
+      <c r="E28" s="19">
         <v>0.62152777777777779</v>
       </c>
-      <c r="F28" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G28" s="4" t="s">
+      <c r="F28" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="G28" s="15" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="6">
+    <row r="29" spans="1:7" s="16" customFormat="1">
+      <c r="A29" s="11">
         <v>46013</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C29" s="8">
+      <c r="C29" s="13">
         <v>0.66527777777777775</v>
       </c>
-      <c r="D29" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E29" s="8">
+      <c r="D29" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" s="13">
         <v>0.83750000000000002</v>
       </c>
-      <c r="F29" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="G29" s="9" t="s">
+      <c r="F29" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="G29" s="26" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="1">
+    <row r="30" spans="1:7" s="16" customFormat="1">
+      <c r="A30" s="17">
         <v>46015</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C30" s="3">
+      <c r="B30" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="19">
         <v>0.4513888888888889</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="E30" s="3">
+      <c r="E30" s="19">
         <v>0.65</v>
       </c>
-      <c r="F30" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G30" s="4" t="s">
+      <c r="F30" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="G30" s="15" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="6">
+    <row r="31" spans="1:7" s="16" customFormat="1">
+      <c r="A31" s="11">
         <v>46015</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C31" s="8">
+      <c r="C31" s="13">
         <v>0.68402777777777779</v>
       </c>
-      <c r="D31" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E31" s="8">
+      <c r="D31" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E31" s="13">
         <v>0.87152777777777779</v>
       </c>
-      <c r="F31" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="G31" s="9" t="s">
+      <c r="F31" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="G31" s="26" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="1">
+    <row r="32" spans="1:7" s="16" customFormat="1">
+      <c r="A32" s="17">
         <v>46058</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="19">
         <v>7.9861111111111105E-2</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="19">
         <v>0.2673611111111111</v>
       </c>
-      <c r="F32" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G32" s="4" t="s">
+      <c r="F32" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="G32" s="15" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="6">
+    <row r="33" spans="1:7" s="16" customFormat="1">
+      <c r="A33" s="11">
         <v>46058</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C33" s="8">
+      <c r="C33" s="13">
         <v>0.44444444444444442</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="E33" s="8">
+      <c r="E33" s="13">
         <v>0.53472222222222221</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="G33" s="9" t="s">
+      <c r="F33" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="G33" s="26" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="1">
+    <row r="34" spans="1:7" s="16" customFormat="1">
+      <c r="A34" s="17">
         <v>46035</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C34" s="3">
+      <c r="B34" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="19">
         <v>0.51736111111111116</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="E34" s="3">
+      <c r="E34" s="19">
         <v>0.7</v>
       </c>
-      <c r="F34" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G34" s="4" t="s">
+      <c r="F34" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="G34" s="15" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="6">
+    <row r="35" spans="1:7" s="16" customFormat="1">
+      <c r="A35" s="11">
         <v>46035</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C35" s="8">
+      <c r="C35" s="13">
         <v>0.72916666666666663</v>
       </c>
-      <c r="D35" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E35" s="8">
+      <c r="D35" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E35" s="13">
         <v>0.87777777777777777</v>
       </c>
-      <c r="F35" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="G35" s="9" t="s">
+      <c r="F35" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="G35" s="26" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
-      <c r="A36" s="1">
+    <row r="36" spans="1:7" s="16" customFormat="1">
+      <c r="A36" s="17">
         <v>45976</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="19">
         <v>0.62708333333333333</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="E36" s="3">
+      <c r="E36" s="19">
         <v>0.79027777777777775</v>
       </c>
-      <c r="F36" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G36" s="4" t="s">
+      <c r="F36" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="G36" s="15" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
-      <c r="A37" s="6">
+    <row r="37" spans="1:7" s="16" customFormat="1">
+      <c r="A37" s="11">
         <v>45976</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B37" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C37" s="8">
+      <c r="C37" s="13">
         <v>0.81388888888888888</v>
       </c>
-      <c r="D37" s="9" t="s">
+      <c r="D37" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="E37" s="8">
+      <c r="E37" s="13">
         <v>1.1805555555555555E-2</v>
       </c>
-      <c r="F37" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="G37" s="9" t="s">
+      <c r="F37" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="G37" s="26" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
-      <c r="A38" s="1">
+    <row r="38" spans="1:7" s="33" customFormat="1">
+      <c r="A38" s="28">
         <v>46014</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C38" s="3">
+      <c r="B38" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="C38" s="30">
         <v>0.47569444444444442</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D38" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="E38" s="3">
+      <c r="E38" s="30">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F38" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G38" s="4" t="s">
+      <c r="F38" s="31" t="s">
+        <v>2</v>
+      </c>
+      <c r="G38" s="32" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
-      <c r="A39" s="6">
+    <row r="39" spans="1:7" s="33" customFormat="1">
+      <c r="A39" s="34">
         <v>46014</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B39" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="C39" s="8">
+      <c r="C39" s="36">
         <v>0.70138888888888884</v>
       </c>
-      <c r="D39" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E39" s="8">
+      <c r="D39" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="E39" s="36">
         <v>0.86805555555555558</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="G39" s="9" t="s">
+      <c r="F39" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="G39" s="38" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
-      <c r="A40" s="6">
+    <row r="40" spans="1:7" s="33" customFormat="1">
+      <c r="A40" s="34">
         <v>46038</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C40" s="8">
+      <c r="C40" s="36">
         <v>0.52083333333333337</v>
       </c>
-      <c r="D40" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E40" s="8">
+      <c r="D40" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="E40" s="36">
         <v>0.65277777777777779</v>
       </c>
-      <c r="F40" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="G40" s="9" t="s">
+      <c r="F40" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="G40" s="38" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
-      <c r="A41" s="1">
+    <row r="41" spans="1:7" s="16" customFormat="1">
+      <c r="A41" s="17">
         <v>46041</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C41" s="3">
+      <c r="B41" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C41" s="19">
         <v>0.41736111111111113</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="D41" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="E41" s="3">
+      <c r="E41" s="19">
         <v>0.61319444444444449</v>
       </c>
-      <c r="F41" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G41" s="4" t="s">
+      <c r="F41" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="G41" s="15" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
-      <c r="A42" s="6">
+    <row r="42" spans="1:7" s="16" customFormat="1">
+      <c r="A42" s="11">
         <v>46041</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="B42" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C42" s="8">
+      <c r="C42" s="13">
         <v>0.67569444444444449</v>
       </c>
-      <c r="D42" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E42" s="8">
+      <c r="D42" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E42" s="13">
         <v>0.87569444444444444</v>
       </c>
-      <c r="F42" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="G42" s="9" t="s">
+      <c r="F42" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="G42" s="26" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
-      <c r="A43" s="1">
+    <row r="43" spans="1:7" s="16" customFormat="1">
+      <c r="A43" s="17">
         <v>46031</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C43" s="3">
+      <c r="B43" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C43" s="19">
         <v>0.42708333333333331</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="D43" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43" s="19">
         <v>0.64722222222222225</v>
       </c>
-      <c r="F43" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G43" s="4" t="s">
+      <c r="F43" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="G43" s="15" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
-      <c r="A44" s="6">
+    <row r="44" spans="1:7" s="16" customFormat="1">
+      <c r="A44" s="11">
         <v>46031</v>
       </c>
-      <c r="B44" s="7" t="s">
+      <c r="B44" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C44" s="8">
+      <c r="C44" s="13">
         <v>0.72291666666666665</v>
       </c>
-      <c r="D44" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E44" s="8">
+      <c r="D44" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E44" s="13">
         <v>0.89722222222222225</v>
       </c>
-      <c r="F44" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="G44" s="9" t="s">
+      <c r="F44" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="G44" s="26" t="s">
         <v>32</v>
       </c>
     </row>

--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\G Drive\Code\flyby\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A462E59-242D-40E8-9DF0-7334A2D096AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ED907D6-14FE-4C69-8E1C-1BDA977DD44A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15744" yWindow="0" windowWidth="7296" windowHeight="12360" tabRatio="592" xr2:uid="{2C9189CC-F63B-451A-B99F-40FF8A7E7B0A}"/>
+    <workbookView xWindow="16332" yWindow="0" windowWidth="6708" windowHeight="12360" tabRatio="592" xr2:uid="{2C9189CC-F63B-451A-B99F-40FF8A7E7B0A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -296,7 +296,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
@@ -304,9 +304,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -317,9 +314,6 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -761,1475 +755,1475 @@
     <col min="7" max="7" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="16" customFormat="1">
-      <c r="A1" s="17">
+    <row r="1" spans="1:7" s="14" customFormat="1">
+      <c r="A1" s="15">
         <v>46067</v>
       </c>
-      <c r="B1" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="19">
+      <c r="B1" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="17">
         <v>9.375E-2</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="19">
+      <c r="E1" s="17">
         <v>0.25416666666666665</v>
       </c>
-      <c r="F1" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="15" t="s">
+      <c r="F1" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="16" customFormat="1">
-      <c r="A2" s="11">
+    <row r="2" spans="1:7" s="14" customFormat="1">
+      <c r="A2" s="9">
         <v>46067</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="11">
         <v>0.28680555555555554</v>
       </c>
-      <c r="D2" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="13">
+      <c r="D2" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="11">
         <v>0.42430555555555555</v>
       </c>
-      <c r="F2" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="G2" s="26" t="s">
+      <c r="F2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="24" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="16" customFormat="1">
-      <c r="A3" s="17">
+    <row r="3" spans="1:7" s="14" customFormat="1">
+      <c r="A3" s="15">
         <v>46075</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="19">
+      <c r="C3" s="17">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="19">
+      <c r="E3" s="17">
         <v>0.2638888888888889</v>
       </c>
-      <c r="F3" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="15" t="s">
+      <c r="F3" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="16" customFormat="1">
-      <c r="A4" s="11">
+    <row r="4" spans="1:7" s="14" customFormat="1">
+      <c r="A4" s="9">
         <v>46075</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="11">
         <v>0.2986111111111111</v>
       </c>
-      <c r="D4" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="13">
+      <c r="D4" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="11">
         <v>0.45069444444444445</v>
       </c>
-      <c r="F4" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="G4" s="26" t="s">
+      <c r="F4" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G4" s="24" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="16" customFormat="1">
-      <c r="A5" s="17">
+    <row r="5" spans="1:7" s="14" customFormat="1">
+      <c r="A5" s="15">
         <v>45998</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="17">
         <v>0.68194444444444446</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="17">
         <v>0.79791666666666672</v>
       </c>
-      <c r="F5" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="G5" s="15" t="s">
+      <c r="F5" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="G5" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="16" customFormat="1">
-      <c r="A6" s="11">
+    <row r="6" spans="1:7" s="14" customFormat="1">
+      <c r="A6" s="9">
         <v>45998</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="11">
         <v>0.82986111111111116</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="D6" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="11">
         <v>0.9375</v>
       </c>
-      <c r="F6" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="G6" s="26" t="s">
+      <c r="F6" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G6" s="24" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="16" customFormat="1">
-      <c r="A7" s="17">
+    <row r="7" spans="1:7" s="14" customFormat="1">
+      <c r="A7" s="15">
         <v>46002</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="17">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="17">
         <v>0.62152777777777779</v>
       </c>
-      <c r="F7" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="G7" s="15" t="s">
+      <c r="F7" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="G7" s="13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" s="16" customFormat="1">
-      <c r="A8" s="11">
+    <row r="8" spans="1:7" s="14" customFormat="1">
+      <c r="A8" s="9">
         <v>46002</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="11">
         <v>0.67013888888888884</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="11">
         <v>0.85416666666666663</v>
       </c>
-      <c r="F8" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="G8" s="26" t="s">
+      <c r="F8" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G8" s="24" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="16" customFormat="1">
-      <c r="A9" s="17">
+    <row r="9" spans="1:7" s="14" customFormat="1">
+      <c r="A9" s="15">
         <v>46064</v>
       </c>
-      <c r="B9" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="19">
+      <c r="B9" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="17">
         <v>8.1944444444444445E-2</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="19">
+      <c r="E9" s="17">
         <v>0.2298611111111111</v>
       </c>
-      <c r="F9" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="G9" s="15" t="s">
+      <c r="F9" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="G9" s="13" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:7" s="16" customFormat="1">
-      <c r="A10" s="11">
+    <row r="10" spans="1:7" s="14" customFormat="1">
+      <c r="A10" s="9">
         <v>46064</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="11">
         <v>0.26111111111111113</v>
       </c>
-      <c r="D10" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="13">
+      <c r="D10" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="11">
         <v>0.38541666666666669</v>
       </c>
-      <c r="F10" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="G10" s="26" t="s">
+      <c r="F10" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G10" s="24" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="16" customFormat="1">
-      <c r="A11" s="17">
+    <row r="11" spans="1:7" s="14" customFormat="1">
+      <c r="A11" s="15">
         <v>46066</v>
       </c>
-      <c r="B11" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="19">
+      <c r="B11" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="17">
         <v>8.1944444444444445E-2</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="17">
         <v>0.22916666666666666</v>
       </c>
-      <c r="F11" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="G11" s="15" t="s">
+      <c r="F11" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="G11" s="13" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:7" s="16" customFormat="1">
-      <c r="A12" s="11">
+    <row r="12" spans="1:7" s="14" customFormat="1">
+      <c r="A12" s="9">
         <v>46066</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="11">
         <v>0.27430555555555558</v>
       </c>
-      <c r="D12" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="13">
+      <c r="D12" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="11">
         <v>0.40972222222222221</v>
       </c>
-      <c r="F12" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="G12" s="26" t="s">
+      <c r="F12" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G12" s="24" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="16" customFormat="1">
-      <c r="A13" s="17">
+    <row r="13" spans="1:7" s="14" customFormat="1">
+      <c r="A13" s="15">
         <v>46070</v>
       </c>
-      <c r="B13" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="19">
+      <c r="B13" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="17">
         <v>9.0277777777777776E-2</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="E13" s="19">
+      <c r="E13" s="17">
         <v>0.25347222222222221</v>
       </c>
-      <c r="F13" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="G13" s="15" t="s">
+      <c r="F13" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="G13" s="13" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:7" s="16" customFormat="1">
-      <c r="A14" s="11">
+    <row r="14" spans="1:7" s="14" customFormat="1">
+      <c r="A14" s="9">
         <v>46070</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="11">
         <v>0.29236111111111113</v>
       </c>
-      <c r="D14" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" s="13">
+      <c r="D14" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="11">
         <v>0.44027777777777777</v>
       </c>
-      <c r="F14" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="G14" s="26" t="s">
+      <c r="F14" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G14" s="24" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:7" s="16" customFormat="1">
-      <c r="A15" s="17">
+    <row r="15" spans="1:7" s="14" customFormat="1">
+      <c r="A15" s="15">
         <v>46071</v>
       </c>
-      <c r="B15" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="19">
+      <c r="B15" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="17">
         <v>7.6388888888888895E-2</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="D15" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="17">
         <v>0.21597222222222223</v>
       </c>
-      <c r="F15" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="G15" s="15" t="s">
+      <c r="F15" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="G15" s="13" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:7" s="16" customFormat="1">
-      <c r="A16" s="11">
+    <row r="16" spans="1:7" s="14" customFormat="1">
+      <c r="A16" s="9">
         <v>46071</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="13">
+      <c r="C16" s="11">
         <v>0.24652777777777779</v>
       </c>
-      <c r="D16" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" s="13">
+      <c r="D16" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="11">
         <v>0.375</v>
       </c>
-      <c r="F16" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="G16" s="26" t="s">
+      <c r="F16" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G16" s="24" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:7" s="16" customFormat="1">
-      <c r="A17" s="17">
+    <row r="17" spans="1:7" s="14" customFormat="1">
+      <c r="A17" s="15">
         <v>46029</v>
       </c>
-      <c r="B17" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="19">
+      <c r="B17" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="17">
         <v>0.3034722222222222</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="19">
+      <c r="E17" s="17">
         <v>0.45277777777777778</v>
       </c>
-      <c r="F17" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="G17" s="15" t="s">
+      <c r="F17" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="G17" s="13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:7" s="16" customFormat="1">
-      <c r="A18" s="11">
+    <row r="18" spans="1:7" s="14" customFormat="1">
+      <c r="A18" s="9">
         <v>46029</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="13">
+      <c r="C18" s="11">
         <v>0.49583333333333335</v>
       </c>
-      <c r="D18" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18" s="13">
+      <c r="D18" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="11">
         <v>0.6381944444444444</v>
       </c>
-      <c r="F18" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="G18" s="26" t="s">
+      <c r="F18" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G18" s="24" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:7" s="16" customFormat="1">
-      <c r="A19" s="17">
+    <row r="19" spans="1:7" s="14" customFormat="1">
+      <c r="A19" s="15">
         <v>46037</v>
       </c>
-      <c r="B19" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" s="19">
+      <c r="B19" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="17">
         <v>0.31527777777777777</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="D19" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="E19" s="19">
+      <c r="E19" s="17">
         <v>0.47708333333333336</v>
       </c>
-      <c r="F19" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="G19" s="15" t="s">
+      <c r="F19" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="G19" s="13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:7" s="16" customFormat="1">
-      <c r="A20" s="11">
+    <row r="20" spans="1:7" s="14" customFormat="1">
+      <c r="A20" s="9">
         <v>46037</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13">
+      <c r="C20" s="11">
         <v>0.50972222222222219</v>
       </c>
-      <c r="D20" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E20" s="13">
+      <c r="D20" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="11">
         <v>0.65</v>
       </c>
-      <c r="F20" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="G20" s="26" t="s">
+      <c r="F20" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G20" s="24" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:7" s="16" customFormat="1">
-      <c r="A21" s="17">
+    <row r="21" spans="1:7" s="14" customFormat="1">
+      <c r="A21" s="15">
         <v>46038</v>
       </c>
-      <c r="B21" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" s="19">
+      <c r="B21" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="17">
         <v>0.30555555555555558</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="19">
+      <c r="E21" s="17">
         <v>0.47916666666666669</v>
       </c>
-      <c r="F21" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="G21" s="15" t="s">
+      <c r="F21" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="G21" s="13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:7" s="16" customFormat="1">
-      <c r="A22" s="17">
+    <row r="22" spans="1:7" s="14" customFormat="1">
+      <c r="A22" s="15">
         <v>46030</v>
       </c>
-      <c r="B22" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" s="19">
+      <c r="B22" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="17">
         <v>0.48958333333333331</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D22" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="E22" s="19">
+      <c r="E22" s="17">
         <v>0.65138888888888891</v>
       </c>
-      <c r="F22" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="G22" s="15" t="s">
+      <c r="F22" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="G22" s="13" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:7" s="16" customFormat="1">
-      <c r="A23" s="11">
+    <row r="23" spans="1:7" s="14" customFormat="1">
+      <c r="A23" s="9">
         <v>46030</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="13">
+      <c r="C23" s="11">
         <v>0.68055555555555558</v>
       </c>
-      <c r="D23" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E23" s="13">
+      <c r="D23" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="11">
         <v>0.82291666666666663</v>
       </c>
-      <c r="F23" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="G23" s="26" t="s">
+      <c r="F23" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G23" s="24" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:7" s="16" customFormat="1">
-      <c r="A24" s="17">
+    <row r="24" spans="1:7" s="14" customFormat="1">
+      <c r="A24" s="15">
         <v>46043</v>
       </c>
-      <c r="B24" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" s="19">
+      <c r="B24" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="17">
         <v>0.44097222222222221</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="E24" s="19">
+      <c r="E24" s="17">
         <v>0.64583333333333337</v>
       </c>
-      <c r="F24" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="G24" s="15" t="s">
+      <c r="F24" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="G24" s="13" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:7" s="16" customFormat="1">
-      <c r="A25" s="11">
+    <row r="25" spans="1:7" s="14" customFormat="1">
+      <c r="A25" s="9">
         <v>46043</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="13">
+      <c r="C25" s="11">
         <v>0.67361111111111116</v>
       </c>
-      <c r="D25" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E25" s="13">
+      <c r="D25" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="11">
         <v>0.85763888888888884</v>
       </c>
-      <c r="F25" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="G25" s="26" t="s">
+      <c r="F25" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G25" s="24" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:7" s="16" customFormat="1">
-      <c r="A26" s="17">
+    <row r="26" spans="1:7" s="14" customFormat="1">
+      <c r="A26" s="15">
         <v>46008</v>
       </c>
-      <c r="B26" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="C26" s="19">
+      <c r="B26" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="17">
         <v>0.67222222222222228</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="D26" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E26" s="19">
+      <c r="E26" s="17">
         <v>0.77847222222222223</v>
       </c>
-      <c r="F26" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="G26" s="15" t="s">
+      <c r="F26" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="G26" s="13" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:7" s="16" customFormat="1">
-      <c r="A27" s="11">
+    <row r="27" spans="1:7" s="14" customFormat="1">
+      <c r="A27" s="9">
         <v>46008</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="13">
+      <c r="C27" s="11">
         <v>0.82361111111111107</v>
       </c>
-      <c r="D27" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E27" s="13">
+      <c r="D27" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" s="11">
         <v>0.92777777777777781</v>
       </c>
-      <c r="F27" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="G27" s="26" t="s">
+      <c r="F27" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G27" s="24" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:7" s="16" customFormat="1">
-      <c r="A28" s="17">
+    <row r="28" spans="1:7" s="14" customFormat="1">
+      <c r="A28" s="15">
         <v>46013</v>
       </c>
-      <c r="B28" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="C28" s="19">
+      <c r="B28" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="17">
         <v>0.43819444444444444</v>
       </c>
-      <c r="D28" s="18" t="s">
+      <c r="D28" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E28" s="19">
+      <c r="E28" s="17">
         <v>0.62152777777777779</v>
       </c>
-      <c r="F28" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="G28" s="15" t="s">
+      <c r="F28" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="G28" s="13" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:7" s="16" customFormat="1">
-      <c r="A29" s="11">
+    <row r="29" spans="1:7" s="14" customFormat="1">
+      <c r="A29" s="9">
         <v>46013</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="B29" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C29" s="13">
+      <c r="C29" s="11">
         <v>0.66527777777777775</v>
       </c>
-      <c r="D29" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E29" s="13">
+      <c r="D29" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" s="11">
         <v>0.83750000000000002</v>
       </c>
-      <c r="F29" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="G29" s="26" t="s">
+      <c r="F29" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G29" s="24" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:7" s="16" customFormat="1">
-      <c r="A30" s="17">
+    <row r="30" spans="1:7" s="14" customFormat="1">
+      <c r="A30" s="15">
         <v>46015</v>
       </c>
-      <c r="B30" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="C30" s="19">
+      <c r="B30" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="17">
         <v>0.4513888888888889</v>
       </c>
-      <c r="D30" s="18" t="s">
+      <c r="D30" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="E30" s="19">
+      <c r="E30" s="17">
         <v>0.65</v>
       </c>
-      <c r="F30" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="G30" s="15" t="s">
+      <c r="F30" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="G30" s="13" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:7" s="16" customFormat="1">
-      <c r="A31" s="11">
+    <row r="31" spans="1:7" s="14" customFormat="1">
+      <c r="A31" s="9">
         <v>46015</v>
       </c>
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C31" s="13">
+      <c r="C31" s="11">
         <v>0.68402777777777779</v>
       </c>
-      <c r="D31" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E31" s="13">
+      <c r="D31" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E31" s="11">
         <v>0.87152777777777779</v>
       </c>
-      <c r="F31" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="G31" s="26" t="s">
+      <c r="F31" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G31" s="24" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:7" s="16" customFormat="1">
-      <c r="A32" s="17">
+    <row r="32" spans="1:7" s="14" customFormat="1">
+      <c r="A32" s="15">
         <v>46058</v>
       </c>
-      <c r="B32" s="18" t="s">
+      <c r="B32" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="C32" s="19">
+      <c r="C32" s="17">
         <v>7.9861111111111105E-2</v>
       </c>
-      <c r="D32" s="18" t="s">
+      <c r="D32" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="E32" s="19">
+      <c r="E32" s="17">
         <v>0.2673611111111111</v>
       </c>
-      <c r="F32" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="G32" s="15" t="s">
+      <c r="F32" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="G32" s="13" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="1:7" s="16" customFormat="1">
-      <c r="A33" s="11">
+    <row r="33" spans="1:7" s="14" customFormat="1">
+      <c r="A33" s="9">
         <v>46058</v>
       </c>
-      <c r="B33" s="12" t="s">
+      <c r="B33" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C33" s="13">
+      <c r="C33" s="11">
         <v>0.44444444444444442</v>
       </c>
-      <c r="D33" s="12" t="s">
+      <c r="D33" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E33" s="13">
+      <c r="E33" s="11">
         <v>0.53472222222222221</v>
       </c>
-      <c r="F33" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="G33" s="26" t="s">
+      <c r="F33" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G33" s="24" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="1:7" s="16" customFormat="1">
-      <c r="A34" s="17">
+    <row r="34" spans="1:7" s="14" customFormat="1">
+      <c r="A34" s="15">
         <v>46035</v>
       </c>
-      <c r="B34" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="C34" s="19">
+      <c r="B34" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="17">
         <v>0.51736111111111116</v>
       </c>
-      <c r="D34" s="18" t="s">
+      <c r="D34" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="E34" s="19">
+      <c r="E34" s="17">
         <v>0.7</v>
       </c>
-      <c r="F34" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="G34" s="15" t="s">
+      <c r="F34" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="G34" s="13" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:7" s="16" customFormat="1">
-      <c r="A35" s="11">
+    <row r="35" spans="1:7" s="14" customFormat="1">
+      <c r="A35" s="9">
         <v>46035</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="B35" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C35" s="13">
+      <c r="C35" s="11">
         <v>0.72916666666666663</v>
       </c>
-      <c r="D35" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E35" s="13">
+      <c r="D35" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E35" s="11">
         <v>0.87777777777777777</v>
       </c>
-      <c r="F35" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="G35" s="26" t="s">
+      <c r="F35" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G35" s="24" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:7" s="16" customFormat="1">
-      <c r="A36" s="17">
+    <row r="36" spans="1:7" s="14" customFormat="1">
+      <c r="A36" s="15">
         <v>45976</v>
       </c>
-      <c r="B36" s="18" t="s">
+      <c r="B36" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C36" s="19">
+      <c r="C36" s="17">
         <v>0.62708333333333333</v>
       </c>
-      <c r="D36" s="15" t="s">
+      <c r="D36" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E36" s="19">
+      <c r="E36" s="17">
         <v>0.79027777777777775</v>
       </c>
-      <c r="F36" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="G36" s="15" t="s">
+      <c r="F36" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="G36" s="13" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:7" s="16" customFormat="1">
-      <c r="A37" s="11">
+    <row r="37" spans="1:7" s="14" customFormat="1">
+      <c r="A37" s="9">
         <v>45976</v>
       </c>
-      <c r="B37" s="12" t="s">
+      <c r="B37" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C37" s="13">
+      <c r="C37" s="11">
         <v>0.81388888888888888</v>
       </c>
-      <c r="D37" s="26" t="s">
+      <c r="D37" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="E37" s="13">
+      <c r="E37" s="11">
         <v>1.1805555555555555E-2</v>
       </c>
-      <c r="F37" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="G37" s="26" t="s">
+      <c r="F37" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G37" s="24" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:7" s="33" customFormat="1">
-      <c r="A38" s="28">
+    <row r="38" spans="1:7" s="31" customFormat="1">
+      <c r="A38" s="26">
         <v>46014</v>
       </c>
-      <c r="B38" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="C38" s="30">
+      <c r="B38" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="C38" s="28">
         <v>0.47569444444444442</v>
       </c>
-      <c r="D38" s="29" t="s">
+      <c r="D38" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="E38" s="30">
+      <c r="E38" s="28">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F38" s="31" t="s">
-        <v>2</v>
-      </c>
-      <c r="G38" s="32" t="s">
+      <c r="F38" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="G38" s="30" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:7" s="33" customFormat="1">
-      <c r="A39" s="34">
+    <row r="39" spans="1:7" s="31" customFormat="1">
+      <c r="A39" s="32">
         <v>46014</v>
       </c>
-      <c r="B39" s="35" t="s">
+      <c r="B39" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="C39" s="36">
+      <c r="C39" s="34">
         <v>0.70138888888888884</v>
       </c>
-      <c r="D39" s="35" t="s">
-        <v>17</v>
-      </c>
-      <c r="E39" s="36">
+      <c r="D39" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="E39" s="34">
         <v>0.86805555555555558</v>
       </c>
-      <c r="F39" s="37" t="s">
-        <v>2</v>
-      </c>
-      <c r="G39" s="38" t="s">
+      <c r="F39" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="G39" s="36" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:7" s="33" customFormat="1">
-      <c r="A40" s="34">
+    <row r="40" spans="1:7" s="31" customFormat="1">
+      <c r="A40" s="32">
         <v>46038</v>
       </c>
-      <c r="B40" s="35" t="s">
+      <c r="B40" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="C40" s="36">
+      <c r="C40" s="34">
         <v>0.52083333333333337</v>
       </c>
-      <c r="D40" s="35" t="s">
-        <v>17</v>
-      </c>
-      <c r="E40" s="36">
+      <c r="D40" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="E40" s="34">
         <v>0.65277777777777779</v>
       </c>
-      <c r="F40" s="37" t="s">
-        <v>2</v>
-      </c>
-      <c r="G40" s="38" t="s">
+      <c r="F40" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="G40" s="36" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="41" spans="1:7" s="16" customFormat="1">
-      <c r="A41" s="17">
+    <row r="41" spans="1:7" s="14" customFormat="1">
+      <c r="A41" s="15">
         <v>46041</v>
       </c>
-      <c r="B41" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="C41" s="19">
+      <c r="B41" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C41" s="17">
         <v>0.41736111111111113</v>
       </c>
-      <c r="D41" s="18" t="s">
+      <c r="D41" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="E41" s="19">
+      <c r="E41" s="17">
         <v>0.61319444444444449</v>
       </c>
-      <c r="F41" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="G41" s="15" t="s">
+      <c r="F41" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="G41" s="13" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="42" spans="1:7" s="16" customFormat="1">
-      <c r="A42" s="11">
+    <row r="42" spans="1:7" s="14" customFormat="1">
+      <c r="A42" s="9">
         <v>46041</v>
       </c>
-      <c r="B42" s="12" t="s">
+      <c r="B42" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C42" s="13">
+      <c r="C42" s="11">
         <v>0.67569444444444449</v>
       </c>
-      <c r="D42" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E42" s="13">
+      <c r="D42" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E42" s="11">
         <v>0.87569444444444444</v>
       </c>
-      <c r="F42" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="G42" s="26" t="s">
+      <c r="F42" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G42" s="24" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="43" spans="1:7" s="16" customFormat="1">
-      <c r="A43" s="17">
+    <row r="43" spans="1:7" s="14" customFormat="1">
+      <c r="A43" s="15">
         <v>46031</v>
       </c>
-      <c r="B43" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="C43" s="19">
+      <c r="B43" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C43" s="17">
         <v>0.42708333333333331</v>
       </c>
-      <c r="D43" s="18" t="s">
+      <c r="D43" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="E43" s="19">
+      <c r="E43" s="17">
         <v>0.64722222222222225</v>
       </c>
-      <c r="F43" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="G43" s="15" t="s">
+      <c r="F43" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="G43" s="13" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="44" spans="1:7" s="16" customFormat="1">
-      <c r="A44" s="11">
+    <row r="44" spans="1:7" s="14" customFormat="1">
+      <c r="A44" s="9">
         <v>46031</v>
       </c>
-      <c r="B44" s="12" t="s">
+      <c r="B44" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C44" s="13">
+      <c r="C44" s="11">
         <v>0.72291666666666665</v>
       </c>
-      <c r="D44" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E44" s="13">
+      <c r="D44" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E44" s="11">
         <v>0.89722222222222225</v>
       </c>
-      <c r="F44" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="G44" s="26" t="s">
+      <c r="F44" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G44" s="24" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
-      <c r="A45" s="1">
+    <row r="45" spans="1:7" s="14" customFormat="1">
+      <c r="A45" s="15">
         <v>46005</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C45" s="3">
+      <c r="B45" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C45" s="17">
         <v>0.47222222222222221</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="D45" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="17">
         <v>0.67361111111111116</v>
       </c>
-      <c r="F45" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G45" s="4" t="s">
+      <c r="F45" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="G45" s="13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
-      <c r="A46" s="6">
+    <row r="46" spans="1:7" s="14" customFormat="1">
+      <c r="A46" s="9">
         <v>46005</v>
       </c>
-      <c r="B46" s="7" t="s">
+      <c r="B46" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C46" s="8">
+      <c r="C46" s="11">
         <v>0.71527777777777779</v>
       </c>
-      <c r="D46" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E46" s="8">
+      <c r="D46" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E46" s="11">
         <v>0.89930555555555558</v>
       </c>
-      <c r="F46" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="G46" s="9" t="s">
+      <c r="F46" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G46" s="24" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:7" s="16" customFormat="1">
-      <c r="A47" s="17">
+    <row r="47" spans="1:7" s="14" customFormat="1">
+      <c r="A47" s="15">
         <v>45971</v>
       </c>
-      <c r="B47" s="18" t="s">
+      <c r="B47" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C47" s="19">
+      <c r="C47" s="17">
         <v>0.4201388888888889</v>
       </c>
-      <c r="D47" s="15" t="s">
+      <c r="D47" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="E47" s="19">
+      <c r="E47" s="17">
         <v>0.63124999999999998</v>
       </c>
-      <c r="F47" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="G47" s="15" t="s">
+      <c r="F47" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="G47" s="13" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:7" s="16" customFormat="1">
-      <c r="A48" s="21">
+    <row r="48" spans="1:7" s="14" customFormat="1">
+      <c r="A48" s="19">
         <v>45971</v>
       </c>
-      <c r="B48" s="22" t="s">
+      <c r="B48" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C48" s="23">
+      <c r="C48" s="21">
         <v>0.67638888888888893</v>
       </c>
-      <c r="D48" s="24" t="s">
+      <c r="D48" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="E48" s="23">
+      <c r="E48" s="21">
         <v>0.88472222222222219</v>
       </c>
-      <c r="F48" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="G48" s="24" t="s">
+      <c r="F48" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="G48" s="22" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:7" s="16" customFormat="1">
-      <c r="A49" s="17">
+    <row r="49" spans="1:7" s="14" customFormat="1">
+      <c r="A49" s="15">
         <v>45975</v>
       </c>
-      <c r="B49" s="18" t="s">
+      <c r="B49" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C49" s="19">
+      <c r="C49" s="17">
         <v>0.4375</v>
       </c>
-      <c r="D49" s="15" t="s">
+      <c r="D49" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="E49" s="19">
+      <c r="E49" s="17">
         <v>0.625</v>
       </c>
-      <c r="F49" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="G49" s="15" t="s">
+      <c r="F49" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="G49" s="13" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:7" s="16" customFormat="1">
-      <c r="A50" s="11">
+    <row r="50" spans="1:7" s="14" customFormat="1">
+      <c r="A50" s="9">
         <v>45975</v>
       </c>
-      <c r="B50" s="12" t="s">
+      <c r="B50" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C50" s="13">
+      <c r="C50" s="11">
         <v>0.66180555555555554</v>
       </c>
-      <c r="D50" s="26" t="s">
+      <c r="D50" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="E50" s="13">
+      <c r="E50" s="11">
         <v>0.83680555555555558</v>
       </c>
-      <c r="F50" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="G50" s="26" t="s">
+      <c r="F50" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G50" s="24" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:7" s="16" customFormat="1">
-      <c r="A51" s="17">
+    <row r="51" spans="1:7" s="14" customFormat="1">
+      <c r="A51" s="15">
         <v>46045</v>
       </c>
-      <c r="B51" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="C51" s="19">
+      <c r="B51" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C51" s="17">
         <v>0.43333333333333335</v>
       </c>
-      <c r="D51" s="18" t="s">
+      <c r="D51" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E51" s="19">
+      <c r="E51" s="17">
         <v>0.61875000000000002</v>
       </c>
-      <c r="F51" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="G51" s="15" t="s">
+      <c r="F51" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="G51" s="13" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:7" s="16" customFormat="1">
-      <c r="A52" s="11">
+    <row r="52" spans="1:7" s="14" customFormat="1">
+      <c r="A52" s="9">
         <v>46045</v>
       </c>
-      <c r="B52" s="12" t="s">
+      <c r="B52" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C52" s="13">
+      <c r="C52" s="11">
         <v>0.65972222222222221</v>
       </c>
-      <c r="D52" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E52" s="13">
+      <c r="D52" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E52" s="11">
         <v>0.82638888888888884</v>
       </c>
-      <c r="F52" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="G52" s="26" t="s">
+      <c r="F52" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G52" s="24" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
-      <c r="A53" s="1">
+    <row r="53" spans="1:7" s="14" customFormat="1">
+      <c r="A53" s="15">
         <v>46009</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C53" s="3">
+      <c r="B53" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C53" s="17">
         <v>0.51666666666666672</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="D53" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="E53" s="3">
+      <c r="E53" s="17">
         <v>0.69444444444444442</v>
       </c>
-      <c r="F53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G53" s="4" t="s">
+      <c r="F53" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="G53" s="13" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
-      <c r="A54" s="6">
+    <row r="54" spans="1:7" s="14" customFormat="1">
+      <c r="A54" s="9">
         <v>46009</v>
       </c>
-      <c r="B54" s="7" t="s">
+      <c r="B54" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C54" s="8">
+      <c r="C54" s="11">
         <v>0.72361111111111109</v>
       </c>
-      <c r="D54" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E54" s="8">
+      <c r="D54" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E54" s="11">
         <v>0.875</v>
       </c>
-      <c r="F54" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="G54" s="9" t="s">
+      <c r="F54" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G54" s="24" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
-      <c r="A55" s="1">
+    <row r="55" spans="1:7" s="14" customFormat="1">
+      <c r="A55" s="15">
         <v>46060</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C55" s="3">
+      <c r="B55" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C55" s="17">
         <v>7.7083333333333337E-2</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="D55" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="E55" s="3">
+      <c r="E55" s="17">
         <v>0.2638888888888889</v>
       </c>
-      <c r="F55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G55" s="4" t="s">
+      <c r="F55" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="G55" s="13" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
-      <c r="A56" s="6">
+    <row r="56" spans="1:7" s="14" customFormat="1">
+      <c r="A56" s="9">
         <v>46060</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="B56" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C56" s="8">
+      <c r="C56" s="11">
         <v>0.32569444444444445</v>
       </c>
-      <c r="D56" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E56" s="8">
+      <c r="D56" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E56" s="11">
         <v>0.48819444444444443</v>
       </c>
-      <c r="F56" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="G56" s="9" t="s">
+      <c r="F56" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G56" s="24" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
-      <c r="A57" s="1">
+    <row r="57" spans="1:7" s="14" customFormat="1">
+      <c r="A57" s="15">
         <v>46065</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C57" s="3">
+      <c r="B57" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C57" s="17">
         <v>7.8472222222222221E-2</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="D57" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="E57" s="3">
+      <c r="E57" s="17">
         <v>0.24652777777777779</v>
       </c>
-      <c r="F57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G57" s="4" t="s">
+      <c r="F57" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="G57" s="13" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
-      <c r="A58" s="6">
+    <row r="58" spans="1:7" s="14" customFormat="1">
+      <c r="A58" s="9">
         <v>46065</v>
       </c>
-      <c r="B58" s="7" t="s">
+      <c r="B58" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C58" s="8">
+      <c r="C58" s="11">
         <v>0.28194444444444444</v>
       </c>
-      <c r="D58" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E58" s="8">
+      <c r="D58" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E58" s="11">
         <v>0.43680555555555556</v>
       </c>
-      <c r="F58" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="G58" s="9" t="s">
+      <c r="F58" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G58" s="24" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
-      <c r="A59" s="1">
+    <row r="59" spans="1:7" s="14" customFormat="1">
+      <c r="A59" s="15">
         <v>46074</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="C59" s="3">
+      <c r="C59" s="17">
         <v>7.2222222222222215E-2</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="D59" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59" s="17">
         <v>0.16875000000000001</v>
       </c>
-      <c r="F59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G59" s="4" t="s">
+      <c r="F59" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="G59" s="13" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
-      <c r="A60" s="6">
+    <row r="60" spans="1:7" s="14" customFormat="1">
+      <c r="A60" s="9">
         <v>46074</v>
       </c>
-      <c r="B60" s="7" t="s">
+      <c r="B60" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C60" s="8">
+      <c r="C60" s="11">
         <v>0.2013888888888889</v>
       </c>
-      <c r="D60" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E60" s="8">
+      <c r="D60" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="E60" s="11">
         <v>0.27500000000000002</v>
       </c>
-      <c r="F60" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="G60" s="9" t="s">
+      <c r="F60" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G60" s="24" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
-      <c r="A61" s="1">
+    <row r="61" spans="1:7" s="14" customFormat="1">
+      <c r="A61" s="15">
         <v>45996</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B61" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C61" s="3">
+      <c r="C61" s="17">
         <v>0.5083333333333333</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="D61" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E61" s="3">
+      <c r="E61" s="17">
         <v>0.67013888888888884</v>
       </c>
-      <c r="F61" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G61" s="4" t="s">
+      <c r="F61" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="G61" s="13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
-      <c r="A62" s="6">
+    <row r="62" spans="1:7" s="14" customFormat="1">
+      <c r="A62" s="9">
         <v>45996</v>
       </c>
-      <c r="B62" s="7" t="s">
+      <c r="B62" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C62" s="8">
+      <c r="C62" s="11">
         <v>0.71527777777777779</v>
       </c>
-      <c r="D62" s="9" t="s">
+      <c r="D62" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="E62" s="8">
+      <c r="E62" s="11">
         <v>0.88124999999999998</v>
       </c>
-      <c r="F62" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="G62" s="9" t="s">
+      <c r="F62" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G62" s="24" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
-      <c r="A63" s="1">
+    <row r="63" spans="1:7" s="14" customFormat="1">
+      <c r="A63" s="15">
         <v>45997</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B63" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C63" s="3">
+      <c r="C63" s="17">
         <v>0.56111111111111112</v>
       </c>
-      <c r="D63" s="4" t="s">
+      <c r="D63" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="E63" s="3">
+      <c r="E63" s="17">
         <v>0.71736111111111112</v>
       </c>
-      <c r="F63" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G63" s="4" t="s">
+      <c r="F63" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="G63" s="13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
-      <c r="A64" s="6">
+    <row r="64" spans="1:7" s="14" customFormat="1">
+      <c r="A64" s="9">
         <v>45997</v>
       </c>
-      <c r="B64" s="7" t="s">
+      <c r="B64" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C64" s="8">
+      <c r="C64" s="11">
         <v>0.75763888888888886</v>
       </c>
-      <c r="D64" s="9" t="s">
+      <c r="D64" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="E64" s="8">
+      <c r="E64" s="11">
         <v>0.93055555555555558</v>
       </c>
-      <c r="F64" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="G64" s="9" t="s">
+      <c r="F64" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G64" s="24" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2239,25 +2233,25 @@
       </c>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
-      <c r="D65" s="4"/>
+      <c r="D65" s="3"/>
       <c r="E65" s="2"/>
-      <c r="F65" s="5" t="s">
+      <c r="F65" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G65" s="4"/>
+      <c r="G65" s="3"/>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="6">
+      <c r="A66" s="5">
         <v>45984</v>
       </c>
-      <c r="B66" s="7"/>
-      <c r="C66" s="7"/>
-      <c r="D66" s="9"/>
-      <c r="E66" s="7"/>
-      <c r="F66" s="10" t="s">
+      <c r="B66" s="6"/>
+      <c r="C66" s="6"/>
+      <c r="D66" s="7"/>
+      <c r="E66" s="6"/>
+      <c r="F66" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="G66" s="9"/>
+      <c r="G66" s="7"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:G66">
